--- a/Tomoscan_pso_interlaced/risultati_timbir_N32_K4_PSO20000.xlsx
+++ b/Tomoscan_pso_interlaced/risultati_timbir_N32_K4_PSO20000.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="MOD360" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UNWRAPPED" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="COUNTS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DELTA_THETA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UNWRAPPED_ACQ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="COUNTS_PSO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DELTA_THETA_PSO" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +422,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_mod360</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -457,13 +457,13 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11.25</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>625</v>
+        <v>2500</v>
       </c>
       <c r="C3" t="n">
-        <v>11.25</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22.5</v>
+        <v>90</v>
       </c>
       <c r="B4" t="n">
-        <v>1250</v>
+        <v>5000</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>90</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>33.75</v>
+        <v>135</v>
       </c>
       <c r="B5" t="n">
-        <v>1875</v>
+        <v>7500</v>
       </c>
       <c r="C5" t="n">
-        <v>33.75</v>
+        <v>135</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="B6" t="n">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56.25</v>
+        <v>225</v>
       </c>
       <c r="B7" t="n">
-        <v>3125</v>
+        <v>12500</v>
       </c>
       <c r="C7" t="n">
-        <v>56.25</v>
+        <v>225</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67.5</v>
+        <v>270</v>
       </c>
       <c r="B8" t="n">
-        <v>3750</v>
+        <v>15000</v>
       </c>
       <c r="C8" t="n">
-        <v>67.5</v>
+        <v>270</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -541,13 +541,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>78.75</v>
+        <v>315</v>
       </c>
       <c r="B9" t="n">
-        <v>4375</v>
+        <v>17500</v>
       </c>
       <c r="C9" t="n">
-        <v>78.75</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -555,13 +555,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90</v>
+        <v>22.5</v>
       </c>
       <c r="B10" t="n">
-        <v>5000</v>
+        <v>1250</v>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>22.5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -569,13 +569,13 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101.25</v>
+        <v>67.5</v>
       </c>
       <c r="B11" t="n">
-        <v>5625</v>
+        <v>3750</v>
       </c>
       <c r="C11" t="n">
-        <v>101.25</v>
+        <v>67.5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123.75</v>
+        <v>157.5</v>
       </c>
       <c r="B13" t="n">
-        <v>6875</v>
+        <v>8750</v>
       </c>
       <c r="C13" t="n">
-        <v>123.75</v>
+        <v>157.5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135</v>
+        <v>202.5</v>
       </c>
       <c r="B14" t="n">
-        <v>7500</v>
+        <v>11250</v>
       </c>
       <c r="C14" t="n">
-        <v>135</v>
+        <v>202.5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>146.25</v>
+        <v>247.5</v>
       </c>
       <c r="B15" t="n">
-        <v>8125</v>
+        <v>13750</v>
       </c>
       <c r="C15" t="n">
-        <v>146.25</v>
+        <v>247.5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>157.5</v>
+        <v>292.5</v>
       </c>
       <c r="B16" t="n">
-        <v>8750</v>
+        <v>16250</v>
       </c>
       <c r="C16" t="n">
-        <v>157.5</v>
+        <v>292.5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -653,13 +653,13 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>168.75</v>
+        <v>337.5</v>
       </c>
       <c r="B17" t="n">
-        <v>9375</v>
+        <v>18750</v>
       </c>
       <c r="C17" t="n">
-        <v>168.75</v>
+        <v>337.5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -667,13 +667,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>180</v>
+        <v>11.25</v>
       </c>
       <c r="B18" t="n">
-        <v>10000</v>
+        <v>625</v>
       </c>
       <c r="C18" t="n">
-        <v>180</v>
+        <v>11.25</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>191.25</v>
+        <v>56.25</v>
       </c>
       <c r="B19" t="n">
-        <v>10625</v>
+        <v>3125</v>
       </c>
       <c r="C19" t="n">
-        <v>191.25</v>
+        <v>56.25</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>202.5</v>
+        <v>101.25</v>
       </c>
       <c r="B20" t="n">
-        <v>11250</v>
+        <v>5625</v>
       </c>
       <c r="C20" t="n">
-        <v>202.5</v>
+        <v>101.25</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>213.75</v>
+        <v>146.25</v>
       </c>
       <c r="B21" t="n">
-        <v>11875</v>
+        <v>8125</v>
       </c>
       <c r="C21" t="n">
-        <v>213.75</v>
+        <v>146.25</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>225</v>
+        <v>191.25</v>
       </c>
       <c r="B22" t="n">
-        <v>12500</v>
+        <v>10625</v>
       </c>
       <c r="C22" t="n">
-        <v>225</v>
+        <v>191.25</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -751,13 +751,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>247.5</v>
+        <v>281.25</v>
       </c>
       <c r="B24" t="n">
-        <v>13750</v>
+        <v>15625</v>
       </c>
       <c r="C24" t="n">
-        <v>247.5</v>
+        <v>281.25</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>258.75</v>
+        <v>326.25</v>
       </c>
       <c r="B25" t="n">
-        <v>14375</v>
+        <v>18125</v>
       </c>
       <c r="C25" t="n">
-        <v>258.75</v>
+        <v>326.25</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -779,13 +779,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>270</v>
+        <v>33.75</v>
       </c>
       <c r="B26" t="n">
-        <v>15000</v>
+        <v>1875</v>
       </c>
       <c r="C26" t="n">
-        <v>270</v>
+        <v>33.75</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -793,13 +793,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>281.25</v>
+        <v>78.75</v>
       </c>
       <c r="B27" t="n">
-        <v>15625</v>
+        <v>4375</v>
       </c>
       <c r="C27" t="n">
-        <v>281.25</v>
+        <v>78.75</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -807,13 +807,13 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>292.5</v>
+        <v>123.75</v>
       </c>
       <c r="B28" t="n">
-        <v>16250</v>
+        <v>6875</v>
       </c>
       <c r="C28" t="n">
-        <v>292.5</v>
+        <v>123.75</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -821,13 +821,13 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>303.75</v>
+        <v>168.75</v>
       </c>
       <c r="B29" t="n">
-        <v>16875</v>
+        <v>9375</v>
       </c>
       <c r="C29" t="n">
-        <v>303.75</v>
+        <v>168.75</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -835,13 +835,13 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>315</v>
+        <v>213.75</v>
       </c>
       <c r="B30" t="n">
-        <v>17500</v>
+        <v>11875</v>
       </c>
       <c r="C30" t="n">
-        <v>315</v>
+        <v>213.75</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -849,13 +849,13 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>326.25</v>
+        <v>258.75</v>
       </c>
       <c r="B31" t="n">
-        <v>18125</v>
+        <v>14375</v>
       </c>
       <c r="C31" t="n">
-        <v>326.25</v>
+        <v>258.75</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -863,13 +863,13 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>337.5</v>
+        <v>303.75</v>
       </c>
       <c r="B32" t="n">
-        <v>18750</v>
+        <v>16875</v>
       </c>
       <c r="C32" t="n">
-        <v>337.5</v>
+        <v>303.75</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>target_deg</t>
+          <t>target_deg_unwrapped_acq</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1137,7 +1137,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>697.5000000000001</v>
+        <v>697.5</v>
       </c>
       <c r="B17" t="n">
         <v>38750</v>
@@ -1146,12 +1146,12 @@
         <v>697.5</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>731.25</v>
+        <v>731.2500000000001</v>
       </c>
       <c r="B18" t="n">
         <v>40625</v>
@@ -1160,7 +1160,7 @@
         <v>731.25</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
     </row>
     <row r="19">
@@ -1179,7 +1179,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>821.25</v>
+        <v>821.2500000000001</v>
       </c>
       <c r="B20" t="n">
         <v>45625</v>
@@ -1188,7 +1188,7 @@
         <v>821.25</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
     </row>
     <row r="21">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>911.25</v>
+        <v>911.2500000000001</v>
       </c>
       <c r="B22" t="n">
         <v>50625</v>
@@ -1216,7 +1216,7 @@
         <v>911.25</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
     </row>
     <row r="23">
@@ -1390,7 +1390,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>theta_unwrapped_deg</t>
+          <t>theta_monotonic_deg</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1621,7 +1621,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>697.5000000000001</v>
+        <v>697.5</v>
       </c>
       <c r="B17" t="n">
         <v>38750</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>731.25</v>
+        <v>731.2500000000001</v>
       </c>
       <c r="B18" t="n">
         <v>40625</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>821.25</v>
+        <v>821.2500000000001</v>
       </c>
       <c r="B20" t="n">
         <v>45625</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>911.25</v>
+        <v>911.2500000000001</v>
       </c>
       <c r="B22" t="n">
         <v>50625</v>
@@ -2097,10 +2097,10 @@
         <v>652.5</v>
       </c>
       <c r="C16" t="n">
-        <v>697.5000000000001</v>
+        <v>697.5</v>
       </c>
       <c r="D16" t="n">
-        <v>45.00000000000011</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -2108,13 +2108,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>697.5000000000001</v>
+        <v>697.5</v>
       </c>
       <c r="C17" t="n">
-        <v>731.25</v>
+        <v>731.2500000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>33.74999999999989</v>
+        <v>33.75000000000011</v>
       </c>
     </row>
     <row r="18">
@@ -2122,13 +2122,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>731.25</v>
+        <v>731.2500000000001</v>
       </c>
       <c r="C18" t="n">
         <v>776.25</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>44.99999999999989</v>
       </c>
     </row>
     <row r="19">
@@ -2139,10 +2139,10 @@
         <v>776.25</v>
       </c>
       <c r="C19" t="n">
-        <v>821.25</v>
+        <v>821.2500000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>45.00000000000011</v>
       </c>
     </row>
     <row r="20">
@@ -2150,13 +2150,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>821.25</v>
+        <v>821.2500000000001</v>
       </c>
       <c r="C20" t="n">
         <v>866.25</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>44.99999999999989</v>
       </c>
     </row>
     <row r="21">
@@ -2167,10 +2167,10 @@
         <v>866.25</v>
       </c>
       <c r="C21" t="n">
-        <v>911.25</v>
+        <v>911.2500000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>45.00000000000011</v>
       </c>
     </row>
     <row r="22">
@@ -2178,13 +2178,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>911.25</v>
+        <v>911.2500000000001</v>
       </c>
       <c r="C22" t="n">
         <v>956.25</v>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>44.99999999999989</v>
       </c>
     </row>
     <row r="23">
